--- a/artfynd/A 73783-2021 artfynd.xlsx
+++ b/artfynd/A 73783-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1429,6 +1429,122 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6623370</v>
+      </c>
+      <c r="B8" t="n">
+        <v>89776</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ej möjlig att validera</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>256756</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blek fingersvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ramaria pallida</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Ricken</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Thoresta, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>645763</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6602219</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Upplands-Bro</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Låssa</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2010-09-23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2010-09-23</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Kalkpåverkad granskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Helen Sundberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Helen Sundberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 73783-2021 artfynd.xlsx
+++ b/artfynd/A 73783-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 73783-2021 artfynd.xlsx
+++ b/artfynd/A 73783-2021 artfynd.xlsx
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1394522</v>
+        <v>1394521</v>
       </c>
       <c r="B2" t="n">
-        <v>90664</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>645763.1948774053</v>
+        <v>645761</v>
       </c>
       <c r="R2" t="n">
-        <v>6602219.059350523</v>
+        <v>6602219</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>2010-09-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2010-09-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1440429</v>
+        <v>1394522</v>
       </c>
       <c r="B3" t="n">
-        <v>90670</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,26 +797,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4368</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -850,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>645734.4481506718</v>
+        <v>645763</v>
       </c>
       <c r="R3" t="n">
-        <v>6602343.861684195</v>
+        <v>6602219</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,19 +863,9 @@
           <t>2010-09-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2010-09-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,15 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1622623</v>
+        <v>1440428</v>
       </c>
       <c r="B4" t="n">
-        <v>90695</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,26 +908,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5448</v>
+        <v>4368</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -976,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>645734.4481506718</v>
+        <v>645794</v>
       </c>
       <c r="R4" t="n">
-        <v>6602343.861684195</v>
+        <v>6602233</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,19 +974,9 @@
           <t>2010-09-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2010-09-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,15 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1440428</v>
+        <v>1440429</v>
       </c>
       <c r="B5" t="n">
-        <v>90670</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1088,7 +1038,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1102,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>645793.6625490342</v>
+        <v>645734</v>
       </c>
       <c r="R5" t="n">
-        <v>6602233.442865415</v>
+        <v>6602344</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,19 +1085,9 @@
           <t>2010-09-23</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2010-09-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1179,42 +1119,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1394521</v>
+        <v>1622623</v>
       </c>
       <c r="B6" t="n">
-        <v>90664</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4366</v>
+        <v>5448</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1228,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>645761.1634529982</v>
+        <v>645734</v>
       </c>
       <c r="R6" t="n">
-        <v>6602218.980531827</v>
+        <v>6602344</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1261,19 +1196,9 @@
           <t>2010-09-23</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2010-09-23</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1308,12 +1233,7 @@
         <v>6623370</v>
       </c>
       <c r="B7" t="n">
-        <v>89863</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ej möjlig att validera</t>
-        </is>
+        <v>91428</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
